--- a/app/backend/Test.xlsx
+++ b/app/backend/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m9/Documents/personal_programming/python/projects/gpt/app/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8112694-68D5-F040-A190-B65F701C6E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8365FAA1-33C9-9541-A928-94781EBDA19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Upper line 
 buttom line</t>
@@ -37,6 +37,15 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>This is test</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can you translate this ? </t>
   </si>
 </sst>
 </file>
@@ -422,17 +431,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="34" customHeight="1" x14ac:dyDescent="0.2">

--- a/app/backend/Test.xlsx
+++ b/app/backend/Test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m9/Documents/personal_programming/python/projects/gpt/app/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8365FAA1-33C9-9541-A928-94781EBDA19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB2DCF2-C49F-F046-9B83-27FD86FEBFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/app/backend/Test.xlsx
+++ b/app/backend/Test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m9/Documents/personal_programming/python/projects/gpt/app/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB2DCF2-C49F-F046-9B83-27FD86FEBFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31525279-7424-B345-B081-415003B96BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Upper line 
 buttom line</t>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t xml:space="preserve">Can you translate this ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mamamia </t>
   </si>
 </sst>
 </file>
@@ -421,32 +424,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
